--- a/python-maps/documentation/CDA2FHIR_elga_general_groups.xlsx
+++ b/python-maps/documentation/CDA2FHIR_elga_general_groups.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DND_GIT_Repos\02_HL7Austria\hl7at_gh_CDA2FHIR\python-maps\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DND_Git_Repos\02_HL7Austria\hl7at_gh_CDA2FHIR\python-maps\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA8C8A-37D9-4D84-82B1-401ED97D6F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FBFB7D-6863-4030-8B06-360077E72356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Misc" sheetId="3" r:id="rId3"/>
     <sheet name="Datentypen" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028" refMode="R1C1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="323">
   <si>
     <t>CDA</t>
   </si>
@@ -134,13 +134,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/composition-status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HL7 AT core ticket erstellen für Composition Profil und Extensions für terminologyDate,formatCode und praticeSettingCode spezifizieren. </t>
-  </si>
-  <si>
-    <t>AG CDA2FHIR (20251117):
-Mapping nicht erforderlich, weil wenn zurück gemapped, dann auf die aktuelle CDA-Leitfadenversion.</t>
   </si>
   <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-practicesetting</t>
@@ -1277,6 +1270,24 @@
       </rPr>
       <t>Misc/AddressCompilation</t>
     </r>
+  </si>
+  <si>
+    <t>Composition.extension('http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-composition-formatCode').valueCodeableConcept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HL7 AT core ticket erstellen für Composition Profil und Extensions für terminologyDate, formatCode spezifizieren. </t>
+  </si>
+  <si>
+    <t>AG CDA2FHIR (20251117):
+Mapping nicht erforderlich, weil wenn zurück gemapped, dann auf die aktuelle CDA-Leitfadenversion.
+Anforderung von Portalprojekt: Information muss gemapped werden, weil sie im Portal angezeigt werden soll.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-formatcode</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/elga-formatcode
+https://termgit.elga.gv.at/CodeSystem/dicom-sopclasses</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1517,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1653,6 +1664,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1664,15 +1685,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2062,47 +2074,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.81640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.453125" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.81640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.26953125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="0.54296875" style="34" customWidth="1"/>
-    <col min="8" max="8" width="25.453125" style="33" customWidth="1"/>
-    <col min="9" max="9" width="29.54296875" style="33" customWidth="1"/>
-    <col min="10" max="10" width="0.54296875" style="34" customWidth="1"/>
-    <col min="11" max="11" width="42.26953125" style="33" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.26953125" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="0.5703125" style="34" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="29.5703125" style="33" customWidth="1"/>
+    <col min="10" max="10" width="0.5703125" style="34" customWidth="1"/>
+    <col min="11" max="11" width="42.28515625" style="33" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.28515625" style="33" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="0.54296875" style="34" customWidth="1"/>
-    <col min="16" max="16384" width="8.7265625" style="42"/>
+    <col min="15" max="15" width="0.5703125" style="34" customWidth="1"/>
+    <col min="16" max="16384" width="8.7109375" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63"/>
       <c r="G1" s="32"/>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="56"/>
+      <c r="I1" s="60"/>
       <c r="J1" s="32"/>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
       <c r="O1" s="32"/>
       <c r="P1" s="41"/>
       <c r="Q1" s="41"/>
@@ -2112,7 +2124,7 @@
       <c r="U1" s="41"/>
       <c r="V1" s="41"/>
     </row>
-    <row r="2" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2160,7 +2172,7 @@
       <c r="U2" s="43"/>
       <c r="V2" s="43"/>
     </row>
-    <row r="3" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
@@ -2169,7 +2181,7 @@
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -2190,16 +2202,16 @@
       <c r="U3" s="44"/>
       <c r="V3" s="44"/>
     </row>
-    <row r="4" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2220,16 +2232,16 @@
       <c r="U4" s="46"/>
       <c r="V4" s="46"/>
     </row>
-    <row r="5" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -2250,7 +2262,7 @@
       <c r="U5" s="46"/>
       <c r="V5" s="46"/>
     </row>
-    <row r="6" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -2259,7 +2271,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -2280,7 +2292,7 @@
       <c r="U6" s="46"/>
       <c r="V6" s="46"/>
     </row>
-    <row r="7" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -2289,7 +2301,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -2310,22 +2322,22 @@
       <c r="U7" s="46"/>
       <c r="V7" s="46"/>
     </row>
-    <row r="8" spans="1:22" s="47" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="14"/>
       <c r="H8" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="14"/>
@@ -2342,7 +2354,7 @@
       <c r="U8" s="46"/>
       <c r="V8" s="46"/>
     </row>
-    <row r="9" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -2351,7 +2363,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
@@ -2374,7 +2386,7 @@
       <c r="U9" s="46"/>
       <c r="V9" s="46"/>
     </row>
-    <row r="10" spans="1:22" s="47" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>19</v>
       </c>
@@ -2383,7 +2395,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>20</v>
@@ -2408,7 +2420,7 @@
       <c r="U10" s="46"/>
       <c r="V10" s="46"/>
     </row>
-    <row r="11" spans="1:22" s="47" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>19</v>
       </c>
@@ -2417,7 +2429,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>20</v>
@@ -2442,7 +2454,7 @@
       <c r="U11" s="46"/>
       <c r="V11" s="46"/>
     </row>
-    <row r="12" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -2451,7 +2463,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
@@ -2474,7 +2486,7 @@
       <c r="U12" s="46"/>
       <c r="V12" s="46"/>
     </row>
-    <row r="13" spans="1:22" s="47" customFormat="1" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" s="47" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -2483,7 +2495,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>24</v>
@@ -2501,7 +2513,7 @@
         <v>27</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>28</v>
@@ -2518,7 +2530,7 @@
       <c r="U13" s="46"/>
       <c r="V13" s="46"/>
     </row>
-    <row r="14" spans="1:22" s="47" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -2527,18 +2539,18 @@
         <v>17</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="18"/>
       <c r="H14" s="4"/>
       <c r="I14" s="20" t="s">
-        <v>30</v>
+        <v>319</v>
       </c>
       <c r="J14" s="18"/>
       <c r="K14" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -2552,26 +2564,32 @@
       <c r="U14" s="46"/>
       <c r="V14" s="46"/>
     </row>
-    <row r="15" spans="1:22" s="47" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" s="47" customFormat="1" ht="195" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+        <v>271</v>
+      </c>
+      <c r="E15" s="59" t="s">
+        <v>321</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>322</v>
+      </c>
       <c r="G15" s="14"/>
       <c r="H15" s="6" t="s">
-        <v>31</v>
+        <v>320</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="14"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="6" t="s">
+        <v>318</v>
+      </c>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
@@ -2584,7 +2602,7 @@
       <c r="U15" s="46"/>
       <c r="V15" s="46"/>
     </row>
-    <row r="16" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
@@ -2593,20 +2611,20 @@
         <v>17</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G16" s="34"/>
       <c r="H16" s="6"/>
       <c r="I16" s="21"/>
       <c r="J16" s="34"/>
       <c r="K16" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -2620,7 +2638,7 @@
       <c r="U16" s="46"/>
       <c r="V16" s="46"/>
     </row>
-    <row r="17" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
@@ -2629,7 +2647,7 @@
         <v>17</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
@@ -2638,7 +2656,7 @@
       <c r="I17" s="35"/>
       <c r="J17" s="18"/>
       <c r="K17" s="17" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
@@ -2652,7 +2670,7 @@
       <c r="U17" s="46"/>
       <c r="V17" s="46"/>
     </row>
-    <row r="18" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -2661,7 +2679,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
@@ -2670,7 +2688,7 @@
       <c r="I18" s="17"/>
       <c r="J18" s="18"/>
       <c r="K18" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -2684,7 +2702,7 @@
       <c r="U18" s="46"/>
       <c r="V18" s="46"/>
     </row>
-    <row r="19" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
@@ -2693,10 +2711,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="18"/>
@@ -2704,7 +2722,7 @@
       <c r="I19" s="17"/>
       <c r="J19" s="18"/>
       <c r="K19" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="6"/>
@@ -2718,7 +2736,7 @@
       <c r="U19" s="46"/>
       <c r="V19" s="46"/>
     </row>
-    <row r="20" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>13</v>
       </c>
@@ -2727,7 +2745,7 @@
         <v>17</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
@@ -2736,7 +2754,7 @@
       <c r="I20" s="17"/>
       <c r="J20" s="24"/>
       <c r="K20" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -2750,7 +2768,7 @@
       <c r="U20" s="46"/>
       <c r="V20" s="46"/>
     </row>
-    <row r="21" spans="1:22" s="47" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" s="47" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
@@ -2759,18 +2777,18 @@
         <v>17</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
       <c r="G21" s="16"/>
       <c r="H21" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="16"/>
       <c r="K21" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -2784,18 +2802,18 @@
       <c r="U21" s="46"/>
       <c r="V21" s="46"/>
     </row>
-    <row r="22" spans="1:22" s="45" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" s="45" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>43</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -2804,7 +2822,7 @@
       <c r="I22" s="10"/>
       <c r="J22" s="11"/>
       <c r="K22" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
@@ -2818,53 +2836,53 @@
       <c r="U22" s="44"/>
       <c r="V22" s="44"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="60"/>
+      <c r="G23" s="56"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="60"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
-      <c r="O23" s="60"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O23" s="56"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="60"/>
+      <c r="G24" s="56"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="60"/>
+      <c r="J24" s="56"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="60"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O24" s="56"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
@@ -2873,204 +2891,204 @@
         <v>17</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="60"/>
+      <c r="G25" s="56"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="60"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-      <c r="O25" s="60"/>
-    </row>
-    <row r="26" spans="1:22" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="O25" s="56"/>
+    </row>
+    <row r="26" spans="1:22" ht="195" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
-      <c r="G26" s="60"/>
+      <c r="G26" s="56"/>
       <c r="H26" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="60"/>
+      <c r="J26" s="56"/>
       <c r="K26" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-      <c r="O26" s="60"/>
-    </row>
-    <row r="27" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O26" s="56"/>
+    </row>
+    <row r="27" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
-      <c r="G27" s="60"/>
+      <c r="G27" s="56"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="60"/>
+      <c r="J27" s="56"/>
       <c r="K27" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
-      <c r="O27" s="60"/>
-    </row>
-    <row r="28" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O27" s="56"/>
+    </row>
+    <row r="28" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
-      <c r="G28" s="60"/>
+      <c r="G28" s="56"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="60"/>
+      <c r="J28" s="56"/>
       <c r="K28" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
-      <c r="O28" s="60"/>
-    </row>
-    <row r="29" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O28" s="56"/>
+    </row>
+    <row r="29" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="60"/>
+      <c r="G29" s="56"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="60"/>
+      <c r="J29" s="56"/>
       <c r="K29" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
-      <c r="O29" s="60"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O29" s="56"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
-      <c r="G30" s="60"/>
+      <c r="G30" s="56"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
-      <c r="J30" s="60"/>
+      <c r="J30" s="56"/>
       <c r="K30" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
-      <c r="O30" s="60"/>
-    </row>
-    <row r="31" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O30" s="56"/>
+    </row>
+    <row r="31" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="60"/>
+      <c r="G31" s="56"/>
       <c r="H31" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I31" s="6"/>
-      <c r="J31" s="60"/>
+      <c r="J31" s="56"/>
       <c r="K31" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
-      <c r="O31" s="60"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O31" s="56"/>
+    </row>
+    <row r="32" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
-      <c r="G32" s="60"/>
+      <c r="G32" s="56"/>
       <c r="H32" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I32" s="6"/>
-      <c r="J32" s="60"/>
+      <c r="J32" s="56"/>
       <c r="K32" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
-      <c r="O32" s="60"/>
-    </row>
-    <row r="33" spans="1:15" ht="87" x14ac:dyDescent="0.35">
+      <c r="O32" s="56"/>
+    </row>
+    <row r="33" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>13</v>
       </c>
@@ -3079,497 +3097,497 @@
         <v>17</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="60"/>
+      <c r="G33" s="56"/>
       <c r="H33" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I33" s="1"/>
-      <c r="J33" s="60"/>
+      <c r="J33" s="56"/>
       <c r="K33" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
-      <c r="O33" s="60"/>
-    </row>
-    <row r="34" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="O33" s="56"/>
+    </row>
+    <row r="34" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="60"/>
+      <c r="G34" s="56"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
-      <c r="J34" s="60"/>
+      <c r="J34" s="56"/>
       <c r="K34" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M34" s="36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N34" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="O34" s="60"/>
-    </row>
-    <row r="35" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="O34" s="56"/>
+    </row>
+    <row r="35" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F35" s="6"/>
-      <c r="G35" s="60"/>
+      <c r="G35" s="56"/>
       <c r="H35" s="37"/>
       <c r="I35" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="J35" s="60"/>
+        <v>65</v>
+      </c>
+      <c r="J35" s="56"/>
       <c r="K35" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L35" s="1"/>
-      <c r="O35" s="60"/>
-    </row>
-    <row r="36" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O35" s="56"/>
+    </row>
+    <row r="36" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
-      <c r="G36" s="60"/>
+      <c r="G36" s="56"/>
       <c r="H36" s="6"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="60"/>
+      <c r="J36" s="56"/>
       <c r="K36" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
-      <c r="O36" s="60"/>
-    </row>
-    <row r="37" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O36" s="56"/>
+    </row>
+    <row r="37" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
-      <c r="G37" s="60"/>
+      <c r="G37" s="56"/>
       <c r="H37" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I37" s="6"/>
-      <c r="J37" s="60"/>
+      <c r="J37" s="56"/>
       <c r="K37" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
-      <c r="O37" s="60"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O37" s="56"/>
+    </row>
+    <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
-      <c r="G38" s="60"/>
+      <c r="G38" s="56"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
-      <c r="J38" s="60"/>
+      <c r="J38" s="56"/>
       <c r="K38" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
-      <c r="O38" s="60"/>
-    </row>
-    <row r="39" spans="1:15" ht="145" x14ac:dyDescent="0.35">
+      <c r="O38" s="56"/>
+    </row>
+    <row r="39" spans="1:15" ht="165" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="G39" s="56"/>
+      <c r="H39" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="I39" s="6"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G39" s="60"/>
-      <c r="H39" s="6" t="s">
+      <c r="L39" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="6" t="s">
+      <c r="M39" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="N39" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="M39" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="O39" s="60"/>
-    </row>
-    <row r="40" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O39" s="56"/>
+    </row>
+    <row r="40" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D40" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G40" s="60"/>
+      <c r="G40" s="56"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="60"/>
+      <c r="J40" s="56"/>
       <c r="K40" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M40" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="N40" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="M40" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="N40" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="O40" s="60"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O40" s="56"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
-      <c r="G41" s="60"/>
+      <c r="G41" s="56"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
-      <c r="J41" s="60"/>
+      <c r="J41" s="56"/>
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
-      <c r="O41" s="60"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O41" s="56"/>
+    </row>
+    <row r="42" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
-      <c r="G42" s="60"/>
+      <c r="G42" s="56"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
-      <c r="J42" s="60"/>
+      <c r="J42" s="56"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
-      <c r="O42" s="60"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O42" s="56"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
-      <c r="G43" s="60"/>
+      <c r="G43" s="56"/>
       <c r="H43" s="37"/>
       <c r="I43" s="6"/>
-      <c r="J43" s="60"/>
+      <c r="J43" s="56"/>
       <c r="K43" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
-      <c r="O43" s="60"/>
-    </row>
-    <row r="44" spans="1:15" ht="174" x14ac:dyDescent="0.35">
+      <c r="O43" s="56"/>
+    </row>
+    <row r="44" spans="1:15" ht="210" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
-      <c r="G44" s="60"/>
+      <c r="G44" s="56"/>
       <c r="H44" s="38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I44" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="J44" s="56"/>
+      <c r="K44" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="L44" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="M44" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="N44" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="J44" s="60"/>
-      <c r="K44" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="L44" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="M44" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="N44" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="O44" s="60"/>
-    </row>
-    <row r="45" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="O44" s="56"/>
+    </row>
+    <row r="45" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
-      <c r="G45" s="60"/>
+      <c r="G45" s="56"/>
       <c r="H45" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I45" s="6"/>
-      <c r="J45" s="60"/>
+      <c r="J45" s="56"/>
       <c r="K45" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
-      <c r="O45" s="60"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O45" s="56"/>
+    </row>
+    <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
-      <c r="G46" s="60"/>
+      <c r="G46" s="56"/>
       <c r="H46" s="17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I46" s="6"/>
-      <c r="J46" s="60"/>
+      <c r="J46" s="56"/>
       <c r="K46" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
-      <c r="O46" s="60"/>
-    </row>
-    <row r="47" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="O46" s="56"/>
+    </row>
+    <row r="47" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="60"/>
+      <c r="G47" s="56"/>
       <c r="H47" s="37"/>
       <c r="I47" s="6"/>
-      <c r="J47" s="60"/>
+      <c r="J47" s="56"/>
       <c r="K47" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
-      <c r="O47" s="60"/>
-    </row>
-    <row r="48" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O47" s="56"/>
+    </row>
+    <row r="48" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
-      <c r="G48" s="60"/>
+      <c r="G48" s="56"/>
       <c r="H48" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I48" s="6"/>
-      <c r="J48" s="60"/>
+      <c r="J48" s="56"/>
       <c r="K48" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
-      <c r="O48" s="60"/>
-    </row>
-    <row r="49" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O48" s="56"/>
+    </row>
+    <row r="49" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
-      <c r="G49" s="60"/>
+      <c r="G49" s="56"/>
       <c r="H49" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I49" s="6"/>
-      <c r="J49" s="60"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
-      <c r="O49" s="60"/>
-    </row>
-    <row r="50" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O49" s="56"/>
+    </row>
+    <row r="50" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
-      <c r="G50" s="60"/>
+      <c r="G50" s="56"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
-      <c r="J50" s="60"/>
+      <c r="J50" s="56"/>
       <c r="K50" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
-      <c r="O50" s="60"/>
-    </row>
-    <row r="51" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O50" s="56"/>
+    </row>
+    <row r="51" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>13</v>
       </c>
@@ -3578,33 +3596,33 @@
         <v>17</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="F51" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E51" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="G51" s="60"/>
+      <c r="G51" s="56"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
-      <c r="J51" s="60"/>
+      <c r="J51" s="56"/>
       <c r="K51" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M51" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="O51" s="60"/>
-    </row>
-    <row r="52" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="O51" s="56"/>
+    </row>
+    <row r="52" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>13</v>
       </c>
@@ -3613,33 +3631,33 @@
         <v>23</v>
       </c>
       <c r="D52" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E52" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="G52" s="60"/>
+      <c r="G52" s="56"/>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
-      <c r="J52" s="60"/>
+      <c r="J52" s="56"/>
       <c r="K52" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M52" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="O52" s="60"/>
-    </row>
-    <row r="53" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="O52" s="56"/>
+    </row>
+    <row r="53" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>13</v>
       </c>
@@ -3648,69 +3666,69 @@
         <v>23</v>
       </c>
       <c r="D53" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E53" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="G53" s="60"/>
+      <c r="G53" s="56"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
-      <c r="J53" s="60"/>
+      <c r="J53" s="56"/>
       <c r="K53" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M53" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="O53" s="60"/>
-    </row>
-    <row r="54" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+      <c r="O53" s="56"/>
+    </row>
+    <row r="54" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
-      <c r="G54" s="60"/>
+      <c r="G54" s="56"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
-      <c r="J54" s="60"/>
+      <c r="J54" s="56"/>
       <c r="K54" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
-      <c r="O54" s="60"/>
-    </row>
-    <row r="55" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="O54" s="56"/>
+    </row>
+    <row r="55" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B55" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
@@ -3731,68 +3749,68 @@
       <c r="U55" s="44"/>
       <c r="V55" s="44"/>
     </row>
-    <row r="56" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
-      <c r="G56" s="60"/>
+      <c r="G56" s="56"/>
       <c r="H56" s="6"/>
       <c r="I56" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="J56" s="60"/>
+        <v>128</v>
+      </c>
+      <c r="J56" s="56"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
-      <c r="O56" s="60"/>
-    </row>
-    <row r="57" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O56" s="56"/>
+    </row>
+    <row r="57" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
-      <c r="G57" s="60"/>
+      <c r="G57" s="56"/>
       <c r="H57" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I57" s="6"/>
-      <c r="J57" s="60"/>
+      <c r="J57" s="56"/>
       <c r="K57" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
-      <c r="O57" s="60"/>
-    </row>
-    <row r="58" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="O57" s="56"/>
+    </row>
+    <row r="58" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
@@ -3813,70 +3831,70 @@
       <c r="U58" s="44"/>
       <c r="V58" s="44"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
-      <c r="G59" s="60"/>
+      <c r="G59" s="56"/>
       <c r="H59" s="6"/>
       <c r="I59" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="J59" s="60"/>
+        <v>134</v>
+      </c>
+      <c r="J59" s="56"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
-      <c r="O59" s="60"/>
-    </row>
-    <row r="60" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O59" s="56"/>
+    </row>
+    <row r="60" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
-      <c r="G60" s="60"/>
+      <c r="G60" s="56"/>
       <c r="H60" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I60" s="6"/>
-      <c r="J60" s="60"/>
+      <c r="J60" s="56"/>
       <c r="K60" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
-      <c r="O60" s="60"/>
-    </row>
-    <row r="61" spans="1:22" s="45" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O60" s="56"/>
+    </row>
+    <row r="61" spans="1:22" s="45" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E61" s="10"/>
       <c r="F61" s="10"/>
@@ -3885,7 +3903,7 @@
       <c r="I61" s="10"/>
       <c r="J61" s="11"/>
       <c r="K61" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L61" s="10"/>
       <c r="M61" s="10"/>
@@ -3899,32 +3917,32 @@
       <c r="U61" s="44"/>
       <c r="V61" s="44"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
-      <c r="G62" s="60"/>
+      <c r="G62" s="56"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
-      <c r="J62" s="60"/>
+      <c r="J62" s="56"/>
       <c r="K62" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
-      <c r="O62" s="60"/>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O62" s="56"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>13</v>
       </c>
@@ -3933,48 +3951,48 @@
         <v>17</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="60"/>
+      <c r="G63" s="56"/>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
-      <c r="J63" s="60"/>
+      <c r="J63" s="56"/>
       <c r="K63" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
-      <c r="O63" s="60"/>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="60"/>
+      <c r="G64" s="56"/>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
-      <c r="J64" s="60"/>
+      <c r="J64" s="56"/>
       <c r="K64" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
-      <c r="O64" s="60"/>
-    </row>
-    <row r="65" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O64" s="56"/>
+    </row>
+    <row r="65" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>13</v>
       </c>
@@ -3983,36 +4001,36 @@
         <v>17</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="60"/>
+      <c r="G65" s="56"/>
       <c r="H65" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I65" s="6"/>
-      <c r="J65" s="60"/>
+      <c r="J65" s="56"/>
       <c r="K65" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
-      <c r="O65" s="60"/>
-    </row>
-    <row r="66" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="O65" s="56"/>
+    </row>
+    <row r="66" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E66" s="10"/>
       <c r="F66" s="10"/>
@@ -4033,35 +4051,35 @@
       <c r="U66" s="44"/>
       <c r="V66" s="44"/>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="1"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
-      <c r="G67" s="60"/>
+      <c r="G67" s="56"/>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
-      <c r="J67" s="60"/>
+      <c r="J67" s="56"/>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
-      <c r="O67" s="60"/>
-    </row>
-    <row r="68" spans="1:22" s="45" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O67" s="56"/>
+    </row>
+    <row r="68" spans="1:22" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
@@ -4070,7 +4088,7 @@
       <c r="I68" s="10"/>
       <c r="J68" s="11"/>
       <c r="K68" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L68" s="10"/>
       <c r="M68" s="10"/>
@@ -4084,40 +4102,40 @@
       <c r="U68" s="44"/>
       <c r="V68" s="44"/>
     </row>
-    <row r="69" spans="1:22" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
-      <c r="G69" s="60"/>
+      <c r="G69" s="56"/>
       <c r="H69" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="56"/>
+      <c r="K69" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M69" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="I69" s="6"/>
-      <c r="J69" s="60"/>
-      <c r="K69" s="6" t="s">
+      <c r="N69" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="L69" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M69" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="N69" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="O69" s="60"/>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O69" s="56"/>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>13</v>
       </c>
@@ -4126,21 +4144,21 @@
         <v>17</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
-      <c r="G70" s="60"/>
+      <c r="G70" s="56"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
-      <c r="J70" s="60"/>
+      <c r="J70" s="56"/>
       <c r="K70" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
-      <c r="O70" s="60"/>
+      <c r="O70" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4167,16 +4185,17 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="I44" r:id="rId1" xr:uid="{91DAE7D1-EB2D-4F26-9D89-8C6E3E1A844C}"/>
+    <hyperlink ref="E15" r:id="rId2" xr:uid="{04566A3A-D698-4098-B875-937AE5DFF17B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA29139-5C73-4E3A-A322-911235CE163A}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4185,47 +4204,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B8B780-8473-4585-855B-E6EE5386FBE0}">
   <dimension ref="A1:V59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.81640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.453125" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.42578125" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="51" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="0.453125" style="34" customWidth="1"/>
-    <col min="8" max="8" width="21.26953125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="0.453125" style="34" customWidth="1"/>
-    <col min="11" max="11" width="40.81640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="0.42578125" style="34" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="0.42578125" style="34" customWidth="1"/>
+    <col min="11" max="11" width="40.85546875" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="40.7265625" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.1796875" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="0.453125" style="34" customWidth="1"/>
-    <col min="16" max="16384" width="10.81640625" style="42"/>
+    <col min="13" max="13" width="40.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="0.42578125" style="34" customWidth="1"/>
+    <col min="16" max="16384" width="10.85546875" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63"/>
       <c r="G1" s="32"/>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="56"/>
+      <c r="I1" s="60"/>
       <c r="J1" s="32"/>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
       <c r="O1" s="32"/>
       <c r="P1" s="41"/>
       <c r="Q1" s="41"/>
@@ -4235,7 +4254,7 @@
       <c r="U1" s="41"/>
       <c r="V1" s="41"/>
     </row>
-    <row r="2" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -4283,16 +4302,16 @@
       <c r="U2" s="43"/>
       <c r="V2" s="43"/>
     </row>
-    <row r="3" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -4301,7 +4320,7 @@
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
       <c r="K3" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
@@ -4315,97 +4334,97 @@
       <c r="U3" s="44"/>
       <c r="V3" s="44"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="60"/>
+      <c r="G4" s="56"/>
       <c r="H4" s="49"/>
       <c r="I4" s="6"/>
       <c r="J4" s="5"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="N4" s="17"/>
-      <c r="O4" s="60"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O4" s="56"/>
+    </row>
+    <row r="5" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="60"/>
+      <c r="G5" s="56"/>
       <c r="H5" s="49"/>
       <c r="I5" s="6"/>
       <c r="J5" s="5"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="N5" s="17"/>
-      <c r="O5" s="60"/>
-    </row>
-    <row r="6" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O5" s="56"/>
+    </row>
+    <row r="6" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="60"/>
+      <c r="G6" s="56"/>
       <c r="H6" s="49"/>
       <c r="I6" s="6"/>
       <c r="J6" s="5"/>
       <c r="K6" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M6" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="N6" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M6" s="33" t="s">
+      <c r="O6" s="56"/>
+    </row>
+    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="O6" s="60"/>
-    </row>
-    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="60"/>
+      <c r="G7" s="56"/>
       <c r="H7" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I7" s="36"/>
       <c r="J7" s="5"/>
@@ -4413,139 +4432,139 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="60"/>
-    </row>
-    <row r="8" spans="1:22" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="O7" s="56"/>
+    </row>
+    <row r="8" spans="1:22" ht="240" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="60"/>
+      <c r="G8" s="56"/>
       <c r="H8" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="5"/>
       <c r="K8" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="60"/>
-    </row>
-    <row r="9" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O8" s="56"/>
+    </row>
+    <row r="9" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G9" s="60"/>
+      <c r="G9" s="56"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="5"/>
       <c r="K9" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="60"/>
-    </row>
-    <row r="10" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O9" s="56"/>
+    </row>
+    <row r="10" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F10" s="6"/>
-      <c r="G10" s="60"/>
+      <c r="G10" s="56"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="5"/>
       <c r="K10" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="60"/>
-    </row>
-    <row r="11" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O10" s="56"/>
+    </row>
+    <row r="11" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-      <c r="G11" s="60"/>
+      <c r="G11" s="56"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="5"/>
       <c r="K11" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="60"/>
-    </row>
-    <row r="12" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="O11" s="56"/>
+    </row>
+    <row r="12" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="60"/>
+      <c r="G12" s="56"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="5"/>
       <c r="K12" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="60"/>
-    </row>
-    <row r="13" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O12" s="56"/>
+    </row>
+    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -4554,34 +4573,34 @@
         <v>17</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-      <c r="G13" s="60"/>
+      <c r="G13" s="56"/>
       <c r="H13" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="5"/>
       <c r="K13" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
-      <c r="O13" s="60"/>
-    </row>
-    <row r="14" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="O13" s="56"/>
+    </row>
+    <row r="14" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C14" s="55"/>
       <c r="D14" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -4590,7 +4609,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="11"/>
       <c r="K14" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
@@ -4604,148 +4623,148 @@
       <c r="U14" s="44"/>
       <c r="V14" s="44"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
-      <c r="G15" s="60"/>
+      <c r="G15" s="56"/>
       <c r="H15" s="49"/>
       <c r="I15" s="6"/>
       <c r="J15" s="5"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="N15" s="17"/>
-      <c r="O15" s="60"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O15" s="56"/>
+    </row>
+    <row r="16" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
-      <c r="G16" s="60"/>
+      <c r="G16" s="56"/>
       <c r="H16" s="49"/>
       <c r="I16" s="6"/>
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="N16" s="17"/>
-      <c r="O16" s="60"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O16" s="56"/>
+    </row>
+    <row r="17" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="60"/>
+      <c r="G17" s="56"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="5"/>
       <c r="K17" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="M17" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="M17" s="33" t="s">
-        <v>185</v>
-      </c>
       <c r="N17" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="O17" s="60"/>
-    </row>
-    <row r="18" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+      <c r="O17" s="56"/>
+    </row>
+    <row r="18" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="60"/>
+      <c r="G18" s="56"/>
       <c r="H18" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="60"/>
-    </row>
-    <row r="19" spans="1:22" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="O18" s="56"/>
+    </row>
+    <row r="19" spans="1:22" ht="240" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="60"/>
+      <c r="G19" s="56"/>
       <c r="H19" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="5"/>
       <c r="K19" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
-      <c r="O19" s="60"/>
-    </row>
-    <row r="20" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+      <c r="O19" s="56"/>
+    </row>
+    <row r="20" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="60"/>
+      <c r="G20" s="56"/>
       <c r="H20" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="5"/>
@@ -4753,58 +4772,58 @@
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
-      <c r="O20" s="60"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O20" s="56"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F21" s="6"/>
-      <c r="G21" s="60"/>
+      <c r="G21" s="56"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
-      <c r="O21" s="60"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O21" s="56"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="60"/>
+      <c r="G22" s="56"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="5"/>
       <c r="K22" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="60"/>
-    </row>
-    <row r="23" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O22" s="56"/>
+    </row>
+    <row r="23" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
@@ -4813,23 +4832,23 @@
         <v>17</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="60"/>
+      <c r="G23" s="56"/>
       <c r="H23" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="5"/>
       <c r="K23" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L23" s="1"/>
-      <c r="O23" s="60"/>
-    </row>
-    <row r="24" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O23" s="56"/>
+    </row>
+    <row r="24" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>13</v>
       </c>
@@ -4838,30 +4857,30 @@
         <v>17</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="60"/>
+      <c r="G24" s="56"/>
       <c r="H24" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="5"/>
       <c r="K24" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="60"/>
-    </row>
-    <row r="25" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="O24" s="56"/>
+    </row>
+    <row r="25" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C25" s="55"/>
       <c r="D25" s="10"/>
@@ -4872,7 +4891,7 @@
       <c r="I25" s="10"/>
       <c r="J25" s="11"/>
       <c r="K25" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
@@ -4886,7 +4905,7 @@
       <c r="U25" s="44"/>
       <c r="V25" s="44"/>
     </row>
-    <row r="26" spans="1:22" s="47" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>13</v>
       </c>
@@ -4895,21 +4914,21 @@
         <v>17</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
-      <c r="G26" s="62"/>
+      <c r="G26" s="58"/>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
       <c r="J26" s="18"/>
       <c r="K26" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-      <c r="O26" s="62"/>
+      <c r="O26" s="58"/>
       <c r="P26" s="46"/>
       <c r="Q26" s="46"/>
       <c r="R26" s="46"/>
@@ -4918,7 +4937,7 @@
       <c r="U26" s="46"/>
       <c r="V26" s="46"/>
     </row>
-    <row r="27" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>13</v>
       </c>
@@ -4927,21 +4946,21 @@
         <v>17</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
-      <c r="G27" s="62"/>
+      <c r="G27" s="58"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
       <c r="J27" s="18"/>
       <c r="K27" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
-      <c r="O27" s="62"/>
+      <c r="O27" s="58"/>
       <c r="P27" s="46"/>
       <c r="Q27" s="46"/>
       <c r="R27" s="46"/>
@@ -4950,16 +4969,16 @@
       <c r="U27" s="46"/>
       <c r="V27" s="46"/>
     </row>
-    <row r="28" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C28" s="55"/>
       <c r="D28" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -4968,7 +4987,7 @@
       <c r="I28" s="10"/>
       <c r="J28" s="11"/>
       <c r="K28" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
@@ -4982,40 +5001,40 @@
       <c r="U28" s="44"/>
       <c r="V28" s="44"/>
     </row>
-    <row r="29" spans="1:22" s="47" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="G29" s="62"/>
+        <v>195</v>
+      </c>
+      <c r="G29" s="58"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="18"/>
       <c r="K29" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="N29" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="O29" s="62"/>
+      <c r="O29" s="58"/>
       <c r="P29" s="46"/>
       <c r="Q29" s="46"/>
       <c r="R29" s="46"/>
@@ -5024,32 +5043,32 @@
       <c r="U29" s="46"/>
       <c r="V29" s="46"/>
     </row>
-    <row r="30" spans="1:22" s="47" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" s="47" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
-      <c r="G30" s="62"/>
+      <c r="G30" s="58"/>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
       <c r="J30" s="18"/>
       <c r="K30" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
-      <c r="O30" s="62"/>
+      <c r="O30" s="58"/>
       <c r="P30" s="46"/>
       <c r="Q30" s="46"/>
       <c r="R30" s="46"/>
@@ -5058,32 +5077,32 @@
       <c r="U30" s="46"/>
       <c r="V30" s="46"/>
     </row>
-    <row r="31" spans="1:22" s="47" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" s="47" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
-      <c r="G31" s="62"/>
+      <c r="G31" s="58"/>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
       <c r="J31" s="18"/>
       <c r="K31" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
-      <c r="O31" s="62"/>
+      <c r="O31" s="58"/>
       <c r="P31" s="46"/>
       <c r="Q31" s="46"/>
       <c r="R31" s="46"/>
@@ -5092,7 +5111,7 @@
       <c r="U31" s="46"/>
       <c r="V31" s="46"/>
     </row>
-    <row r="32" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>13</v>
       </c>
@@ -5101,21 +5120,21 @@
         <v>17</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
-      <c r="G32" s="62"/>
+      <c r="G32" s="58"/>
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
       <c r="J32" s="18"/>
       <c r="K32" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
-      <c r="O32" s="62"/>
+      <c r="O32" s="58"/>
       <c r="P32" s="46"/>
       <c r="Q32" s="46"/>
       <c r="R32" s="46"/>
@@ -5124,7 +5143,7 @@
       <c r="U32" s="46"/>
       <c r="V32" s="46"/>
     </row>
-    <row r="33" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>13</v>
       </c>
@@ -5133,21 +5152,21 @@
         <v>17</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
-      <c r="G33" s="62"/>
+      <c r="G33" s="58"/>
       <c r="H33" s="17"/>
       <c r="I33" s="17"/>
       <c r="J33" s="18"/>
       <c r="K33" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
-      <c r="O33" s="62"/>
+      <c r="O33" s="58"/>
       <c r="P33" s="46"/>
       <c r="Q33" s="46"/>
       <c r="R33" s="46"/>
@@ -5156,30 +5175,30 @@
       <c r="U33" s="46"/>
       <c r="V33" s="46"/>
     </row>
-    <row r="34" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
-      <c r="G34" s="62"/>
+      <c r="G34" s="58"/>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
       <c r="J34" s="18"/>
       <c r="K34" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
-      <c r="O34" s="62"/>
+      <c r="O34" s="58"/>
       <c r="P34" s="46"/>
       <c r="Q34" s="46"/>
       <c r="R34" s="46"/>
@@ -5188,7 +5207,7 @@
       <c r="U34" s="46"/>
       <c r="V34" s="46"/>
     </row>
-    <row r="35" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>13</v>
       </c>
@@ -5197,21 +5216,21 @@
         <v>17</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
-      <c r="G35" s="62"/>
+      <c r="G35" s="58"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="18"/>
       <c r="K35" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L35" s="39"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
-      <c r="O35" s="62"/>
+      <c r="O35" s="58"/>
       <c r="P35" s="46"/>
       <c r="Q35" s="46"/>
       <c r="R35" s="46"/>
@@ -5220,32 +5239,32 @@
       <c r="U35" s="46"/>
       <c r="V35" s="46"/>
     </row>
-    <row r="36" spans="1:22" s="47" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
-      <c r="G36" s="62"/>
+      <c r="G36" s="58"/>
       <c r="H36" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="18"/>
       <c r="K36" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
-      <c r="O36" s="62"/>
+      <c r="O36" s="58"/>
       <c r="P36" s="46"/>
       <c r="Q36" s="46"/>
       <c r="R36" s="46"/>
@@ -5254,12 +5273,12 @@
       <c r="U36" s="46"/>
       <c r="V36" s="46"/>
     </row>
-    <row r="37" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C37" s="55"/>
       <c r="D37" s="10"/>
@@ -5270,7 +5289,7 @@
       <c r="I37" s="10"/>
       <c r="J37" s="11"/>
       <c r="K37" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L37" s="10"/>
       <c r="M37" s="10"/>
@@ -5284,30 +5303,30 @@
       <c r="U37" s="44"/>
       <c r="V37" s="44"/>
     </row>
-    <row r="38" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D38" s="50" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
-      <c r="G38" s="62"/>
+      <c r="G38" s="58"/>
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
       <c r="J38" s="18"/>
       <c r="K38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
-      <c r="O38" s="62"/>
+      <c r="O38" s="58"/>
       <c r="P38" s="46"/>
       <c r="Q38" s="46"/>
       <c r="R38" s="46"/>
@@ -5316,20 +5335,20 @@
       <c r="U38" s="46"/>
       <c r="V38" s="46"/>
     </row>
-    <row r="39" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
-      <c r="G39" s="62"/>
+      <c r="G39" s="58"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
       <c r="J39" s="18"/>
@@ -5337,7 +5356,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
-      <c r="O39" s="62"/>
+      <c r="O39" s="58"/>
       <c r="P39" s="46"/>
       <c r="Q39" s="46"/>
       <c r="R39" s="46"/>
@@ -5346,30 +5365,30 @@
       <c r="U39" s="46"/>
       <c r="V39" s="46"/>
     </row>
-    <row r="40" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
-      <c r="G40" s="62"/>
+      <c r="G40" s="58"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
       <c r="J40" s="18"/>
       <c r="K40" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
-      <c r="O40" s="62"/>
+      <c r="O40" s="58"/>
       <c r="P40" s="46"/>
       <c r="Q40" s="46"/>
       <c r="R40" s="46"/>
@@ -5378,7 +5397,7 @@
       <c r="U40" s="46"/>
       <c r="V40" s="46"/>
     </row>
-    <row r="41" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>13</v>
       </c>
@@ -5387,21 +5406,21 @@
         <v>17</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
-      <c r="G41" s="62"/>
+      <c r="G41" s="58"/>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="18"/>
       <c r="K41" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
-      <c r="O41" s="62"/>
+      <c r="O41" s="58"/>
       <c r="P41" s="46"/>
       <c r="Q41" s="46"/>
       <c r="R41" s="46"/>
@@ -5410,40 +5429,40 @@
       <c r="U41" s="46"/>
       <c r="V41" s="46"/>
     </row>
-    <row r="42" spans="1:22" s="47" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" s="47" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="G42" s="62"/>
+        <v>218</v>
+      </c>
+      <c r="G42" s="58"/>
       <c r="H42" s="17"/>
       <c r="I42" s="17"/>
       <c r="J42" s="18"/>
       <c r="K42" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="O42" s="62"/>
+        <v>220</v>
+      </c>
+      <c r="O42" s="58"/>
       <c r="P42" s="46"/>
       <c r="Q42" s="46"/>
       <c r="R42" s="46"/>
@@ -5452,32 +5471,32 @@
       <c r="U42" s="46"/>
       <c r="V42" s="46"/>
     </row>
-    <row r="43" spans="1:22" s="47" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
-      <c r="G43" s="62"/>
+      <c r="G43" s="58"/>
       <c r="H43" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="18"/>
       <c r="K43" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
-      <c r="O43" s="62"/>
+      <c r="O43" s="58"/>
       <c r="P43" s="46"/>
       <c r="Q43" s="46"/>
       <c r="R43" s="46"/>
@@ -5486,16 +5505,16 @@
       <c r="U43" s="46"/>
       <c r="V43" s="46"/>
     </row>
-    <row r="44" spans="1:22" s="45" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C44" s="55"/>
       <c r="D44" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -5504,7 +5523,7 @@
       <c r="I44" s="10"/>
       <c r="J44" s="11"/>
       <c r="K44" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
@@ -5518,20 +5537,20 @@
       <c r="U44" s="44"/>
       <c r="V44" s="44"/>
     </row>
-    <row r="45" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D45" s="50" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
-      <c r="G45" s="62"/>
+      <c r="G45" s="58"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="18"/>
@@ -5539,7 +5558,7 @@
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
-      <c r="O45" s="62"/>
+      <c r="O45" s="58"/>
       <c r="P45" s="46"/>
       <c r="Q45" s="46"/>
       <c r="R45" s="46"/>
@@ -5548,32 +5567,32 @@
       <c r="U45" s="46"/>
       <c r="V45" s="46"/>
     </row>
-    <row r="46" spans="1:22" s="47" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" s="47" customFormat="1" ht="240" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
-      <c r="G46" s="62"/>
+      <c r="G46" s="58"/>
       <c r="H46" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="18"/>
       <c r="K46" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
-      <c r="O46" s="62"/>
+      <c r="O46" s="58"/>
       <c r="P46" s="46"/>
       <c r="Q46" s="46"/>
       <c r="R46" s="46"/>
@@ -5582,38 +5601,38 @@
       <c r="U46" s="46"/>
       <c r="V46" s="46"/>
     </row>
-    <row r="47" spans="1:22" s="47" customFormat="1" ht="261" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" s="47" customFormat="1" ht="300" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B47" s="17"/>
       <c r="C47" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
-      <c r="G47" s="62"/>
+      <c r="G47" s="58"/>
       <c r="H47" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="18"/>
       <c r="K47" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M47" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="N47" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M47" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="N47" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="O47" s="62"/>
+      <c r="O47" s="58"/>
       <c r="P47" s="46"/>
       <c r="Q47" s="46"/>
       <c r="R47" s="46"/>
@@ -5622,32 +5641,32 @@
       <c r="U47" s="46"/>
       <c r="V47" s="46"/>
     </row>
-    <row r="48" spans="1:22" s="47" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" s="47" customFormat="1" ht="300" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="15"/>
-      <c r="G48" s="62"/>
+      <c r="G48" s="58"/>
       <c r="H48" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="18"/>
       <c r="K48" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
-      <c r="O48" s="62"/>
+      <c r="O48" s="58"/>
       <c r="P48" s="46"/>
       <c r="Q48" s="46"/>
       <c r="R48" s="46"/>
@@ -5656,42 +5675,42 @@
       <c r="U48" s="46"/>
       <c r="V48" s="46"/>
     </row>
-    <row r="49" spans="1:22" s="47" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" s="47" customFormat="1" ht="240" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" s="17"/>
       <c r="C49" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="G49" s="62"/>
+        <v>218</v>
+      </c>
+      <c r="G49" s="58"/>
       <c r="H49" s="17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I49" s="17"/>
       <c r="J49" s="18"/>
       <c r="K49" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="O49" s="62"/>
+        <v>220</v>
+      </c>
+      <c r="O49" s="58"/>
       <c r="P49" s="46"/>
       <c r="Q49" s="46"/>
       <c r="R49" s="46"/>
@@ -5700,7 +5719,7 @@
       <c r="U49" s="46"/>
       <c r="V49" s="46"/>
     </row>
-    <row r="50" spans="1:22" s="47" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>13</v>
       </c>
@@ -5709,21 +5728,21 @@
         <v>17</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
-      <c r="G50" s="62"/>
+      <c r="G50" s="58"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
       <c r="J50" s="18"/>
       <c r="K50" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
-      <c r="O50" s="62"/>
+      <c r="O50" s="58"/>
       <c r="P50" s="46"/>
       <c r="Q50" s="46"/>
       <c r="R50" s="46"/>
@@ -5732,32 +5751,32 @@
       <c r="U50" s="46"/>
       <c r="V50" s="46"/>
     </row>
-    <row r="51" spans="1:22" s="47" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="62"/>
+      <c r="G51" s="58"/>
       <c r="H51" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="18"/>
       <c r="K51" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
-      <c r="O51" s="62"/>
+      <c r="O51" s="58"/>
       <c r="P51" s="46"/>
       <c r="Q51" s="46"/>
       <c r="R51" s="46"/>
@@ -5766,16 +5785,16 @@
       <c r="U51" s="46"/>
       <c r="V51" s="46"/>
     </row>
-    <row r="52" spans="1:22" s="45" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" s="45" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C52" s="55"/>
       <c r="D52" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
@@ -5784,7 +5803,7 @@
       <c r="I52" s="10"/>
       <c r="J52" s="11"/>
       <c r="K52" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
@@ -5798,7 +5817,7 @@
       <c r="U52" s="44"/>
       <c r="V52" s="44"/>
     </row>
-    <row r="53" spans="1:22" s="47" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" s="47" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>13</v>
       </c>
@@ -5807,13 +5826,13 @@
         <v>16</v>
       </c>
       <c r="D53" s="50" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
-      <c r="G53" s="62"/>
+      <c r="G53" s="58"/>
       <c r="H53" s="17" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="18"/>
@@ -5821,7 +5840,7 @@
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
-      <c r="O53" s="62"/>
+      <c r="O53" s="58"/>
       <c r="P53" s="46"/>
       <c r="Q53" s="46"/>
       <c r="R53" s="46"/>
@@ -5830,30 +5849,30 @@
       <c r="U53" s="46"/>
       <c r="V53" s="46"/>
     </row>
-    <row r="54" spans="1:22" s="47" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
-      <c r="G54" s="62"/>
+      <c r="G54" s="58"/>
       <c r="H54" s="17"/>
       <c r="I54" s="17"/>
       <c r="J54" s="18"/>
       <c r="K54" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
-      <c r="O54" s="62"/>
+      <c r="O54" s="58"/>
       <c r="P54" s="46"/>
       <c r="Q54" s="46"/>
       <c r="R54" s="46"/>
@@ -5862,42 +5881,42 @@
       <c r="U54" s="46"/>
       <c r="V54" s="46"/>
     </row>
-    <row r="55" spans="1:22" s="47" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B55" s="17"/>
       <c r="C55" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E55" s="53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="G55" s="62"/>
+        <v>228</v>
+      </c>
+      <c r="G55" s="58"/>
       <c r="H55" s="30" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="18"/>
       <c r="K55" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L55" s="17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M55" s="52" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N55" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="O55" s="62"/>
+        <v>231</v>
+      </c>
+      <c r="O55" s="58"/>
       <c r="P55" s="54"/>
       <c r="Q55" s="54"/>
       <c r="R55" s="54"/>
@@ -5906,32 +5925,32 @@
       <c r="U55" s="54"/>
       <c r="V55" s="54"/>
     </row>
-    <row r="56" spans="1:22" s="47" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" s="47" customFormat="1" ht="300" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
-      <c r="G56" s="62"/>
+      <c r="G56" s="58"/>
       <c r="H56" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="18"/>
       <c r="K56" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
-      <c r="O56" s="62"/>
+      <c r="O56" s="58"/>
       <c r="P56" s="46"/>
       <c r="Q56" s="46"/>
       <c r="R56" s="46"/>
@@ -5940,32 +5959,32 @@
       <c r="U56" s="46"/>
       <c r="V56" s="46"/>
     </row>
-    <row r="57" spans="1:22" s="47" customFormat="1" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" s="47" customFormat="1" ht="240" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
-      <c r="G57" s="62"/>
+      <c r="G57" s="58"/>
       <c r="H57" s="17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I57" s="17"/>
       <c r="J57" s="18"/>
       <c r="K57" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
-      <c r="O57" s="62"/>
+      <c r="O57" s="58"/>
       <c r="P57" s="46"/>
       <c r="Q57" s="46"/>
       <c r="R57" s="46"/>
@@ -5974,7 +5993,7 @@
       <c r="U57" s="46"/>
       <c r="V57" s="46"/>
     </row>
-    <row r="58" spans="1:22" s="47" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>13</v>
       </c>
@@ -5983,21 +6002,21 @@
         <v>17</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
-      <c r="G58" s="62"/>
+      <c r="G58" s="58"/>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
       <c r="J58" s="18"/>
       <c r="K58" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="62"/>
+      <c r="O58" s="58"/>
       <c r="P58" s="46"/>
       <c r="Q58" s="46"/>
       <c r="R58" s="46"/>
@@ -6006,32 +6025,32 @@
       <c r="U58" s="46"/>
       <c r="V58" s="46"/>
     </row>
-    <row r="59" spans="1:22" s="47" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="15"/>
-      <c r="G59" s="62"/>
+      <c r="G59" s="58"/>
       <c r="H59" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I59" s="6"/>
       <c r="J59" s="18"/>
       <c r="K59" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
-      <c r="O59" s="62"/>
+      <c r="O59" s="58"/>
       <c r="P59" s="46"/>
       <c r="Q59" s="46"/>
       <c r="R59" s="46"/>
@@ -6080,50 +6099,50 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA20CACE-D623-47E8-8614-7F4543534309}">
   <dimension ref="A1:P7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.81640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.453125" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="0.453125" style="34" customWidth="1"/>
-    <col min="9" max="9" width="24.453125" style="33" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="0.453125" style="34" customWidth="1"/>
-    <col min="12" max="12" width="21.81640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="48.7265625" style="33" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="40.54296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="0.453125" style="34" customWidth="1"/>
-    <col min="17" max="16384" width="11.453125" style="8"/>
+    <col min="1" max="1" width="9.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="0.42578125" style="34" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" style="33" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.42578125" style="34" customWidth="1"/>
+    <col min="12" max="12" width="21.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="40.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="0.42578125" style="34" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="56"/>
       <c r="I1" s="48"/>
       <c r="J1" s="48"/>
       <c r="K1" s="32"/>
-      <c r="L1" s="57" t="s">
+      <c r="L1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="60"/>
-    </row>
-    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="56"/>
+    </row>
+    <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -6134,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -6145,7 +6164,7 @@
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="61"/>
+      <c r="H2" s="57"/>
       <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
@@ -6165,14 +6184,14 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="61"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P2" s="57"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="10"/>
@@ -6184,102 +6203,102 @@
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
       <c r="L3" s="10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="31" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4" s="62"/>
+        <v>195</v>
+      </c>
+      <c r="H4" s="58"/>
       <c r="I4" s="6"/>
       <c r="J4" s="17"/>
       <c r="K4" s="18"/>
       <c r="L4" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="O4" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="O4" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="P4" s="62"/>
-    </row>
-    <row r="5" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="P4" s="58"/>
+    </row>
+    <row r="5" spans="1:16" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="H5" s="62"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="6"/>
       <c r="J5" s="17"/>
       <c r="K5" s="18"/>
       <c r="L5" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="O5" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="P5" s="62"/>
-    </row>
-    <row r="6" spans="1:16" ht="116" x14ac:dyDescent="0.35">
+      <c r="P5" s="58"/>
+    </row>
+    <row r="6" spans="1:16" ht="150" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
-      <c r="H6" s="62"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="18"/>
@@ -6287,35 +6306,35 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
-      <c r="P6" s="62"/>
-    </row>
-    <row r="7" spans="1:16" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="P6" s="58"/>
+    </row>
+    <row r="7" spans="1:16" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="31" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
-      <c r="H7" s="62"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="18"/>
       <c r="L7" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
-      <c r="P7" s="62"/>
+      <c r="P7" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="2">
